--- a/man_power/sample_data/sample_forecast_upload.xlsx
+++ b/man_power/sample_data/sample_forecast_upload.xlsx
@@ -423,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S10"/>
+  <dimension ref="A1:U10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -445,6 +445,8 @@
     <col width="20" customWidth="1" min="17" max="17"/>
     <col width="20" customWidth="1" min="18" max="18"/>
     <col width="20" customWidth="1" min="19" max="19"/>
+    <col width="20" customWidth="1" min="20" max="20"/>
+    <col width="20" customWidth="1" min="21" max="21"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -535,10 +537,20 @@
       </c>
       <c r="R1" s="1" t="inlineStr">
         <is>
+          <t>AHT Change Percentage</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>AHT Change Period</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
           <t>Forecast Horizon Months</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="U1" s="1" t="inlineStr">
         <is>
           <t>Remarks</t>
         </is>
@@ -609,11 +621,19 @@
         </is>
       </c>
       <c r="R2" t="n">
+        <v>-2</v>
+      </c>
+      <c r="S2" t="inlineStr">
+        <is>
+          <t>Monthly</t>
+        </is>
+      </c>
+      <c r="T2" t="n">
         <v>12</v>
       </c>
-      <c r="S2" t="inlineStr">
-        <is>
-          <t>Valid - 5% monthly growth, 12 months</t>
+      <c r="U2" t="inlineStr">
+        <is>
+          <t>Valid - volume +5%/month, AHT -2%/month (automation)</t>
         </is>
       </c>
     </row>
@@ -672,12 +692,12 @@
           <t>Quarterly</t>
         </is>
       </c>
-      <c r="R3" t="n">
+      <c r="T3" t="n">
         <v>24</v>
       </c>
-      <c r="S3" t="inlineStr">
-        <is>
-          <t>Valid - deterministic, 10% per quarter</t>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Valid - volume growth only</t>
         </is>
       </c>
     </row>
@@ -737,20 +757,20 @@
       <c r="O4" t="n">
         <v>10000</v>
       </c>
-      <c r="P4" t="n">
-        <v>8</v>
-      </c>
-      <c r="Q4" t="inlineStr">
-        <is>
-          <t>Yearly</t>
-        </is>
-      </c>
       <c r="R4" t="n">
-        <v>36</v>
+        <v>10</v>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>Valid - 8% per year, 3 years</t>
+          <t>Quarterly</t>
+        </is>
+      </c>
+      <c r="T4" t="n">
+        <v>12</v>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Valid - AHT +10%/quarter only (new compliance checks)</t>
         </is>
       </c>
     </row>
@@ -801,9 +821,9 @@
           <t>No</t>
         </is>
       </c>
-      <c r="S5" t="inlineStr">
-        <is>
-          <t>Valid - no growth projection</t>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Valid - no projection</t>
         </is>
       </c>
     </row>
@@ -868,11 +888,19 @@
         </is>
       </c>
       <c r="R6" t="n">
+        <v>3</v>
+      </c>
+      <c r="S6" t="inlineStr">
+        <is>
+          <t>Half-Yearly</t>
+        </is>
+      </c>
+      <c r="T6" t="n">
         <v>24</v>
       </c>
-      <c r="S6" t="inlineStr">
-        <is>
-          <t>Valid - 3% decline per half-year</t>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Valid - volume falls, AHT rises</t>
         </is>
       </c>
     </row>
@@ -941,9 +969,17 @@
         </is>
       </c>
       <c r="R7" t="n">
+        <v>0</v>
+      </c>
+      <c r="S7" t="inlineStr">
+        <is>
+          <t>Monthly</t>
+        </is>
+      </c>
+      <c r="T7" t="n">
         <v>12</v>
       </c>
-      <c r="S7" t="inlineStr">
+      <c r="U7" t="inlineStr">
         <is>
           <t>INVALID - negative volume</t>
         </is>
@@ -1014,9 +1050,17 @@
         </is>
       </c>
       <c r="R8" t="n">
+        <v>0</v>
+      </c>
+      <c r="S8" t="inlineStr">
+        <is>
+          <t>Monthly</t>
+        </is>
+      </c>
+      <c r="T8" t="n">
         <v>12</v>
       </c>
-      <c r="S8" t="inlineStr">
+      <c r="U8" t="inlineStr">
         <is>
           <t>INVALID - process belongs to HR</t>
         </is>
@@ -1079,19 +1123,27 @@
         <v>10000</v>
       </c>
       <c r="P9" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>Daily</t>
+          <t>Monthly</t>
         </is>
       </c>
       <c r="R9" t="n">
+        <v>-100</v>
+      </c>
+      <c r="S9" t="inlineStr">
+        <is>
+          <t>Monthly</t>
+        </is>
+      </c>
+      <c r="T9" t="n">
         <v>12</v>
       </c>
-      <c r="S9" t="inlineStr">
-        <is>
-          <t>INVALID - growth too high</t>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>INVALID - AHT change must be above -100%</t>
         </is>
       </c>
     </row>
@@ -1126,7 +1178,7 @@
         </is>
       </c>
       <c r="H10" t="n">
-        <v>25</v>
+        <v>8</v>
       </c>
       <c r="I10" t="n">
         <v>5</v>
@@ -1149,22 +1201,30 @@
         <v>15</v>
       </c>
       <c r="O10" t="n">
-        <v>500</v>
+        <v>10000</v>
       </c>
       <c r="P10" t="n">
         <v>5</v>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
+          <t>Monthly</t>
+        </is>
+      </c>
+      <c r="R10" t="n">
+        <v>4</v>
+      </c>
+      <c r="S10" t="inlineStr">
+        <is>
           <t>Fortnightly</t>
         </is>
       </c>
-      <c r="R10" t="n">
-        <v>72</v>
-      </c>
-      <c r="S10" t="inlineStr">
-        <is>
-          <t>INVALID - simulations, growth period, horizon</t>
+      <c r="T10" t="n">
+        <v>12</v>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>INVALID - AHT change period</t>
         </is>
       </c>
     </row>

--- a/man_power/sample_data/sample_forecast_upload.xlsx
+++ b/man_power/sample_data/sample_forecast_upload.xlsx
@@ -423,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U10"/>
+  <dimension ref="A1:U6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -477,32 +477,32 @@
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>Average Processing Time</t>
+          <t>AHT Minutes</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>Time Unit</t>
+          <t>Working Hours Per Day</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>Working Hours Per Day</t>
+          <t>Working Days Per Week</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>Working Days Per Week</t>
+          <t>Working Days Per Month</t>
         </is>
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>Working Days Per Month</t>
+          <t>Contingency Percentage</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
         <is>
-          <t>Contingency Percentage</t>
+          <t>Total Time Spent Hours</t>
         </is>
       </c>
       <c r="L1" s="1" t="inlineStr">
@@ -517,7 +517,7 @@
       </c>
       <c r="N1" s="1" t="inlineStr">
         <is>
-          <t>Processing Time Variation Percentage</t>
+          <t>AHT Variation Percentage</t>
         </is>
       </c>
       <c r="O1" s="1" t="inlineStr">
@@ -576,26 +576,21 @@
         <v>2200</v>
       </c>
       <c r="E2" t="n">
-        <v>3</v>
+        <v>2.5</v>
       </c>
       <c r="F2" t="n">
         <v>10</v>
       </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>Minutes</t>
-        </is>
+      <c r="G2" t="n">
+        <v>8</v>
       </c>
       <c r="H2" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="I2" t="n">
-        <v>5</v>
+        <v>22</v>
       </c>
       <c r="J2" t="n">
-        <v>22</v>
-      </c>
-      <c r="K2" t="n">
         <v>15</v>
       </c>
       <c r="L2" t="inlineStr">
@@ -633,7 +628,7 @@
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>Valid - volume +5%/month, AHT -2%/month (automation)</t>
+          <t>Measured AHT, decimal FTE</t>
         </is>
       </c>
     </row>
@@ -654,29 +649,21 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>500</v>
+        <v>400.5</v>
       </c>
       <c r="E3" t="n">
-        <v>3</v>
-      </c>
-      <c r="F3" t="n">
-        <v>12</v>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>Minutes</t>
-        </is>
+        <v>4</v>
+      </c>
+      <c r="G3" t="n">
+        <v>8</v>
       </c>
       <c r="H3" t="n">
-        <v>8</v>
+        <v>5.5</v>
       </c>
       <c r="I3" t="n">
-        <v>5</v>
+        <v>23.83</v>
       </c>
       <c r="J3" t="n">
-        <v>22</v>
-      </c>
-      <c r="K3" t="n">
         <v>15</v>
       </c>
       <c r="L3" t="inlineStr">
@@ -697,179 +684,173 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>Valid - volume growth only</t>
+          <t>AHT blank = calculated</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Human Resources</t>
+          <t>HR -TA</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Payroll Processing</t>
+          <t>Offer Rollout</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Monthly</t>
+          <t>Yearly</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>5000</v>
+        <v>6305</v>
       </c>
       <c r="E4" t="n">
-        <v>1</v>
+        <v>180</v>
       </c>
       <c r="F4" t="n">
-        <v>90</v>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>Seconds</t>
-        </is>
+        <v>120</v>
+      </c>
+      <c r="G4" t="n">
+        <v>8</v>
       </c>
       <c r="H4" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="I4" t="n">
-        <v>5</v>
+        <v>22</v>
       </c>
       <c r="J4" t="n">
-        <v>22</v>
-      </c>
-      <c r="K4" t="n">
         <v>15</v>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="M4" t="n">
-        <v>10</v>
-      </c>
-      <c r="N4" t="n">
-        <v>15</v>
-      </c>
-      <c r="O4" t="n">
-        <v>10000</v>
-      </c>
-      <c r="R4" t="n">
-        <v>10</v>
-      </c>
-      <c r="S4" t="inlineStr">
-        <is>
-          <t>Quarterly</t>
-        </is>
-      </c>
-      <c r="T4" t="n">
-        <v>12</v>
+          <t>No</t>
+        </is>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>Valid - AHT +10%/quarter only (new compliance checks)</t>
+          <t>Measured AHT 120 min</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Procurement</t>
+          <t>Finance</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Vendor Registration</t>
+          <t>Bank Reconciliation</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Quarterly</t>
+          <t>Daily</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>600</v>
+        <v>150</v>
       </c>
       <c r="E5" t="n">
-        <v>1</v>
-      </c>
-      <c r="F5" t="n">
-        <v>25</v>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>Minutes</t>
-        </is>
+        <v>0</v>
+      </c>
+      <c r="G5" t="n">
+        <v>8</v>
       </c>
       <c r="H5" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="I5" t="n">
-        <v>5</v>
+        <v>22</v>
       </c>
       <c r="J5" t="n">
-        <v>22</v>
-      </c>
-      <c r="K5" t="n">
         <v>15</v>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="M5" t="n">
+        <v>10</v>
+      </c>
+      <c r="N5" t="n">
+        <v>15</v>
+      </c>
+      <c r="O5" t="n">
+        <v>10000</v>
+      </c>
+      <c r="P5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>Monthly</t>
+        </is>
+      </c>
+      <c r="R5" t="n">
+        <v>0</v>
+      </c>
+      <c r="S5" t="inlineStr">
+        <is>
+          <t>Monthly</t>
+        </is>
+      </c>
+      <c r="T5" t="n">
+        <v>12</v>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>Valid - no projection</t>
+          <t>INVALID - FTE 0 and no AHT</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Customer Service</t>
+          <t>Finance</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Complaint Handling</t>
+          <t>GST Return Filing</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Yearly</t>
+          <t>Monthly</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>40000</v>
+        <v>-5</v>
       </c>
       <c r="E6" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F6" t="n">
+        <v>60</v>
+      </c>
+      <c r="G6" t="n">
+        <v>8</v>
+      </c>
+      <c r="H6" t="n">
+        <v>5</v>
+      </c>
+      <c r="I6" t="n">
+        <v>22</v>
+      </c>
+      <c r="J6" t="n">
         <v>15</v>
       </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>Minutes</t>
-        </is>
-      </c>
-      <c r="H6" t="n">
-        <v>8</v>
-      </c>
-      <c r="I6" t="n">
-        <v>5</v>
-      </c>
-      <c r="J6" t="n">
-        <v>22</v>
-      </c>
-      <c r="K6" t="n">
-        <v>20</v>
-      </c>
-      <c r="L6" t="inlineStr"/>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="M6" t="n">
         <v>10</v>
       </c>
@@ -880,351 +861,27 @@
         <v>10000</v>
       </c>
       <c r="P6" t="n">
-        <v>-3</v>
+        <v>0</v>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>Half-Yearly</t>
+          <t>Monthly</t>
         </is>
       </c>
       <c r="R6" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>Half-Yearly</t>
+          <t>Monthly</t>
         </is>
       </c>
       <c r="T6" t="n">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>Valid - volume falls, AHT rises</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>Finance</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>Bank Reconciliation</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Daily</t>
-        </is>
-      </c>
-      <c r="D7" t="n">
-        <v>-50</v>
-      </c>
-      <c r="E7" t="n">
-        <v>2</v>
-      </c>
-      <c r="F7" t="n">
-        <v>6</v>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>Minutes</t>
-        </is>
-      </c>
-      <c r="H7" t="n">
-        <v>8</v>
-      </c>
-      <c r="I7" t="n">
-        <v>5</v>
-      </c>
-      <c r="J7" t="n">
-        <v>22</v>
-      </c>
-      <c r="K7" t="n">
-        <v>15</v>
-      </c>
-      <c r="L7" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="M7" t="n">
-        <v>10</v>
-      </c>
-      <c r="N7" t="n">
-        <v>15</v>
-      </c>
-      <c r="O7" t="n">
-        <v>10000</v>
-      </c>
-      <c r="P7" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q7" t="inlineStr">
-        <is>
-          <t>Monthly</t>
-        </is>
-      </c>
-      <c r="R7" t="n">
-        <v>0</v>
-      </c>
-      <c r="S7" t="inlineStr">
-        <is>
-          <t>Monthly</t>
-        </is>
-      </c>
-      <c r="T7" t="n">
-        <v>12</v>
-      </c>
-      <c r="U7" t="inlineStr">
-        <is>
           <t>INVALID - negative volume</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>Finance</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>Payroll Processing</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Monthly</t>
-        </is>
-      </c>
-      <c r="D8" t="n">
-        <v>1000</v>
-      </c>
-      <c r="E8" t="n">
-        <v>2</v>
-      </c>
-      <c r="F8" t="n">
-        <v>5</v>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>Minutes</t>
-        </is>
-      </c>
-      <c r="H8" t="n">
-        <v>8</v>
-      </c>
-      <c r="I8" t="n">
-        <v>5</v>
-      </c>
-      <c r="J8" t="n">
-        <v>22</v>
-      </c>
-      <c r="K8" t="n">
-        <v>15</v>
-      </c>
-      <c r="L8" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="M8" t="n">
-        <v>10</v>
-      </c>
-      <c r="N8" t="n">
-        <v>15</v>
-      </c>
-      <c r="O8" t="n">
-        <v>10000</v>
-      </c>
-      <c r="P8" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q8" t="inlineStr">
-        <is>
-          <t>Monthly</t>
-        </is>
-      </c>
-      <c r="R8" t="n">
-        <v>0</v>
-      </c>
-      <c r="S8" t="inlineStr">
-        <is>
-          <t>Monthly</t>
-        </is>
-      </c>
-      <c r="T8" t="n">
-        <v>12</v>
-      </c>
-      <c r="U8" t="inlineStr">
-        <is>
-          <t>INVALID - process belongs to HR</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>Human Resources</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>Leave Management</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Daily</t>
-        </is>
-      </c>
-      <c r="D9" t="n">
-        <v>300</v>
-      </c>
-      <c r="E9" t="n">
-        <v>1</v>
-      </c>
-      <c r="F9" t="n">
-        <v>75</v>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>Seconds</t>
-        </is>
-      </c>
-      <c r="H9" t="n">
-        <v>8</v>
-      </c>
-      <c r="I9" t="n">
-        <v>5</v>
-      </c>
-      <c r="J9" t="n">
-        <v>22</v>
-      </c>
-      <c r="K9" t="n">
-        <v>15</v>
-      </c>
-      <c r="L9" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="M9" t="n">
-        <v>10</v>
-      </c>
-      <c r="N9" t="n">
-        <v>15</v>
-      </c>
-      <c r="O9" t="n">
-        <v>10000</v>
-      </c>
-      <c r="P9" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q9" t="inlineStr">
-        <is>
-          <t>Monthly</t>
-        </is>
-      </c>
-      <c r="R9" t="n">
-        <v>-100</v>
-      </c>
-      <c r="S9" t="inlineStr">
-        <is>
-          <t>Monthly</t>
-        </is>
-      </c>
-      <c r="T9" t="n">
-        <v>12</v>
-      </c>
-      <c r="U9" t="inlineStr">
-        <is>
-          <t>INVALID - AHT change must be above -100%</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>Human Resources</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>Employee Onboarding</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Monthly</t>
-        </is>
-      </c>
-      <c r="D10" t="n">
-        <v>120</v>
-      </c>
-      <c r="E10" t="n">
-        <v>2</v>
-      </c>
-      <c r="F10" t="n">
-        <v>2</v>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>Hours</t>
-        </is>
-      </c>
-      <c r="H10" t="n">
-        <v>8</v>
-      </c>
-      <c r="I10" t="n">
-        <v>5</v>
-      </c>
-      <c r="J10" t="n">
-        <v>22</v>
-      </c>
-      <c r="K10" t="n">
-        <v>15</v>
-      </c>
-      <c r="L10" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="M10" t="n">
-        <v>10</v>
-      </c>
-      <c r="N10" t="n">
-        <v>15</v>
-      </c>
-      <c r="O10" t="n">
-        <v>10000</v>
-      </c>
-      <c r="P10" t="n">
-        <v>5</v>
-      </c>
-      <c r="Q10" t="inlineStr">
-        <is>
-          <t>Monthly</t>
-        </is>
-      </c>
-      <c r="R10" t="n">
-        <v>4</v>
-      </c>
-      <c r="S10" t="inlineStr">
-        <is>
-          <t>Fortnightly</t>
-        </is>
-      </c>
-      <c r="T10" t="n">
-        <v>12</v>
-      </c>
-      <c r="U10" t="inlineStr">
-        <is>
-          <t>INVALID - AHT change period</t>
         </is>
       </c>
     </row>
